--- a/Sheet_ori.xlsx
+++ b/Sheet_ori.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\ElswordInfo\DarkElfMarket\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00599DAD-4DF2-49B7-A55F-C7B1CDA839E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C82752C-F053-430D-93E9-0A5B78E644BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5280" yWindow="3045" windowWidth="21600" windowHeight="11385" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="21600" windowHeight="11385" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表2" sheetId="2" r:id="rId1"/>
     <sheet name="List" sheetId="1" r:id="rId2"/>
     <sheet name="0926紀錄" sheetId="4" r:id="rId3"/>
+    <sheet name="0930紀錄" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -514,8 +515,81 @@
 </comments>
 </file>
 
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>USER</author>
+  </authors>
+  <commentList>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{1CAFBDAE-E2BE-4212-B11A-DF916D4F1275}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>USER:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>假設一件成裝</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">140 7000NT
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="細明體"/>
+            <family val="3"/>
+            <charset val="136"/>
+          </rPr>
+          <t>黑色碎片換算台幣</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>50</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="61">
   <si>
     <t>【黑暗精靈黑市 - 可能出現的拍賣品】</t>
   </si>
@@ -714,6 +788,10 @@
   </si>
   <si>
     <t>ED比值</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>彈匣選擇箱</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -727,7 +805,7 @@
     <numFmt numFmtId="177" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="178" formatCode="m&quot;月&quot;d&quot;日&quot;"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -814,6 +892,13 @@
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -853,7 +938,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -944,6 +1029,7 @@
     <xf numFmtId="177" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="177" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -2595,17 +2681,19 @@
     </row>
     <row r="11" spans="1:11" ht="16.5">
       <c r="A11" s="7" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B11" s="20">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>MIN(D11:K11)</f>
+        <v>2205000000</v>
       </c>
       <c r="C11" s="21">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="D11" s="23"/>
+        <f>MAX(D11:K11)</f>
+        <v>2205000000</v>
+      </c>
+      <c r="D11" s="23">
+        <v>2205000000</v>
+      </c>
       <c r="E11" s="33"/>
       <c r="F11" s="33"/>
       <c r="G11" s="33"/>
@@ -2837,14 +2925,11 @@
       </c>
       <c r="B21" s="20">
         <f t="shared" si="0"/>
-        <v>2205000000</v>
+        <v>0</v>
       </c>
       <c r="C21" s="21">
         <f t="shared" si="1"/>
-        <v>2205000000</v>
-      </c>
-      <c r="D21" s="23">
-        <v>2205000000</v>
+        <v>0</v>
       </c>
       <c r="E21" s="33"/>
       <c r="F21" s="33"/>
@@ -3475,6 +3560,1211 @@
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6E10D7E-FF9F-428F-A996-237F2DB3161D}">
+  <dimension ref="A1:S78"/>
+  <sheetFormatPr defaultRowHeight="15.75"/>
+  <cols>
+    <col min="1" max="1" width="40.5703125" customWidth="1"/>
+    <col min="2" max="2" width="19.85546875" customWidth="1"/>
+    <col min="3" max="3" width="18.5703125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="6" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="8" width="18.28515625" style="6" customWidth="1"/>
+    <col min="9" max="10" width="18.28515625" customWidth="1"/>
+    <col min="11" max="11" width="18.140625" customWidth="1"/>
+    <col min="12" max="13" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19">
+      <c r="B1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="6"/>
+    </row>
+    <row r="2" spans="1:19" ht="16.5">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="38">
+        <v>46295</v>
+      </c>
+      <c r="E2" s="39">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="16.5">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="24"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="32"/>
+      <c r="G3" s="32"/>
+      <c r="H3" s="32"/>
+      <c r="I3" s="32"/>
+      <c r="J3" s="32"/>
+      <c r="K3" s="32"/>
+    </row>
+    <row r="4" spans="1:19" ht="16.5">
+      <c r="A4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="20">
+        <f>MIN(D4:K4)</f>
+        <v>100000000</v>
+      </c>
+      <c r="C4" s="21">
+        <f>MAX(D4:K4)</f>
+        <v>1736437500</v>
+      </c>
+      <c r="D4" s="22">
+        <v>1736437500</v>
+      </c>
+      <c r="E4" s="23">
+        <v>926100000</v>
+      </c>
+      <c r="F4" s="33">
+        <v>840000000</v>
+      </c>
+      <c r="G4" s="33">
+        <v>525000000</v>
+      </c>
+      <c r="H4" s="33">
+        <v>292526061</v>
+      </c>
+      <c r="I4" s="33">
+        <v>100000000</v>
+      </c>
+      <c r="J4" s="33">
+        <v>630000000</v>
+      </c>
+      <c r="K4" s="33">
+        <v>765768937</v>
+      </c>
+      <c r="L4" s="33">
+        <v>347287500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="16.5">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="20">
+        <f t="shared" ref="B5:B41" si="0">MIN(D5:K5)</f>
+        <v>121550625</v>
+      </c>
+      <c r="C5" s="21">
+        <f t="shared" ref="C5:C41" si="1">MAX(D5:K5)</f>
+        <v>513781804</v>
+      </c>
+      <c r="D5" s="23">
+        <v>121550625</v>
+      </c>
+      <c r="E5" s="33">
+        <v>513781804</v>
+      </c>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+    </row>
+    <row r="6" spans="1:19" ht="16.5">
+      <c r="A6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="20">
+        <f t="shared" si="0"/>
+        <v>315000000</v>
+      </c>
+      <c r="C6" s="21">
+        <f t="shared" si="1"/>
+        <v>814447312</v>
+      </c>
+      <c r="D6" s="23">
+        <v>752456250</v>
+      </c>
+      <c r="E6" s="33">
+        <v>752456250</v>
+      </c>
+      <c r="F6" s="33">
+        <v>814447312</v>
+      </c>
+      <c r="G6" s="33">
+        <v>703550211</v>
+      </c>
+      <c r="H6" s="33">
+        <v>315000000</v>
+      </c>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+    </row>
+    <row r="7" spans="1:19" ht="16.5">
+      <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="20">
+        <f t="shared" si="0"/>
+        <v>52500000</v>
+      </c>
+      <c r="C7" s="21">
+        <f t="shared" si="1"/>
+        <v>231525000</v>
+      </c>
+      <c r="D7" s="23">
+        <v>52500000</v>
+      </c>
+      <c r="E7" s="33">
+        <v>231525000</v>
+      </c>
+      <c r="F7" s="33">
+        <v>115762500</v>
+      </c>
+      <c r="G7" s="33"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="33"/>
+    </row>
+    <row r="8" spans="1:19" ht="16.5">
+      <c r="A8" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="20">
+        <f>MIN(D8:O8)</f>
+        <v>11025000</v>
+      </c>
+      <c r="C8" s="21">
+        <f t="shared" si="1"/>
+        <v>231525000</v>
+      </c>
+      <c r="D8" s="23">
+        <v>15513279</v>
+      </c>
+      <c r="E8" s="33">
+        <v>231525000</v>
+      </c>
+      <c r="F8" s="33">
+        <v>17103389</v>
+      </c>
+      <c r="G8" s="33">
+        <v>32250982</v>
+      </c>
+      <c r="H8" s="33">
+        <v>60000000</v>
+      </c>
+      <c r="I8" s="33">
+        <v>20789274</v>
+      </c>
+      <c r="J8" s="33">
+        <v>50000000</v>
+      </c>
+      <c r="K8" s="33">
+        <v>26594196</v>
+      </c>
+      <c r="L8" s="33">
+        <v>26250000</v>
+      </c>
+      <c r="M8" s="33">
+        <v>136500000</v>
+      </c>
+      <c r="N8" s="33">
+        <v>11025000</v>
+      </c>
+      <c r="O8" s="33">
+        <v>13400955</v>
+      </c>
+      <c r="P8" s="33">
+        <v>11576250</v>
+      </c>
+      <c r="Q8" s="33">
+        <v>100000000</v>
+      </c>
+      <c r="R8" s="33">
+        <v>12249999</v>
+      </c>
+      <c r="S8" s="33"/>
+    </row>
+    <row r="9" spans="1:19" ht="16.5">
+      <c r="A9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="20">
+        <f t="shared" si="0"/>
+        <v>630000000</v>
+      </c>
+      <c r="C9" s="21">
+        <f t="shared" si="1"/>
+        <v>1000000000</v>
+      </c>
+      <c r="D9" s="23">
+        <v>1000000000</v>
+      </c>
+      <c r="E9" s="33">
+        <v>630000000</v>
+      </c>
+      <c r="F9" s="33"/>
+      <c r="G9" s="33"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="33"/>
+    </row>
+    <row r="10" spans="1:19" ht="16.5">
+      <c r="A10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" s="34"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+    </row>
+    <row r="11" spans="1:19" ht="16.5">
+      <c r="A11" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="20">
+        <f>MIN(D11:K11)</f>
+        <v>551250000</v>
+      </c>
+      <c r="C11" s="21">
+        <f>MAX(D11:K11)</f>
+        <v>2756250000</v>
+      </c>
+      <c r="D11" s="33">
+        <v>2756250000</v>
+      </c>
+      <c r="E11" s="40">
+        <v>711134520</v>
+      </c>
+      <c r="F11" s="33">
+        <v>551250000</v>
+      </c>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+    </row>
+    <row r="12" spans="1:19" ht="16.5">
+      <c r="A12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="20">
+        <f t="shared" si="0"/>
+        <v>620531284</v>
+      </c>
+      <c r="C12" s="21">
+        <f t="shared" si="1"/>
+        <v>2625000000</v>
+      </c>
+      <c r="D12" s="23">
+        <v>2625000000</v>
+      </c>
+      <c r="E12" s="33">
+        <v>1914422343</v>
+      </c>
+      <c r="F12" s="33">
+        <v>718342527</v>
+      </c>
+      <c r="G12" s="33">
+        <v>620531284</v>
+      </c>
+      <c r="H12" s="33">
+        <v>1000000000</v>
+      </c>
+      <c r="I12" s="33"/>
+      <c r="J12" s="33"/>
+      <c r="K12" s="33"/>
+    </row>
+    <row r="13" spans="1:19" ht="16.5">
+      <c r="A13" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="20">
+        <f t="shared" si="0"/>
+        <v>630000000</v>
+      </c>
+      <c r="C13" s="21">
+        <f t="shared" si="1"/>
+        <v>2205000000</v>
+      </c>
+      <c r="D13" s="23">
+        <v>1181964353</v>
+      </c>
+      <c r="E13" s="33">
+        <v>1340095640</v>
+      </c>
+      <c r="F13" s="33">
+        <v>1276281562</v>
+      </c>
+      <c r="G13" s="33">
+        <v>1200000000</v>
+      </c>
+      <c r="H13" s="33">
+        <v>1466005160</v>
+      </c>
+      <c r="I13" s="33">
+        <v>2205000000</v>
+      </c>
+      <c r="J13" s="33">
+        <v>1000637680</v>
+      </c>
+      <c r="K13" s="33">
+        <v>630000000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="16.5">
+      <c r="A14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="20">
+        <f t="shared" si="0"/>
+        <v>140710041</v>
+      </c>
+      <c r="C14" s="21">
+        <f t="shared" si="1"/>
+        <v>1155000000</v>
+      </c>
+      <c r="D14" s="23">
+        <v>240661916</v>
+      </c>
+      <c r="E14" s="33">
+        <v>700000000</v>
+      </c>
+      <c r="F14" s="33">
+        <v>565694738</v>
+      </c>
+      <c r="G14" s="33">
+        <v>525000000</v>
+      </c>
+      <c r="H14" s="33">
+        <v>989965796</v>
+      </c>
+      <c r="I14" s="33">
+        <v>1155000000</v>
+      </c>
+      <c r="J14" s="33">
+        <v>140710041</v>
+      </c>
+      <c r="K14" s="33"/>
+    </row>
+    <row r="15" spans="1:19" ht="16.5">
+      <c r="A15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="20">
+        <f t="shared" si="0"/>
+        <v>36465187</v>
+      </c>
+      <c r="C15" s="21">
+        <f t="shared" si="1"/>
+        <v>136500000</v>
+      </c>
+      <c r="D15" s="23">
+        <v>36465187</v>
+      </c>
+      <c r="E15" s="33">
+        <v>136500000</v>
+      </c>
+      <c r="F15" s="33"/>
+      <c r="G15" s="33"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="33"/>
+      <c r="K15" s="33"/>
+    </row>
+    <row r="16" spans="1:19" ht="16.5">
+      <c r="A16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C16" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D16" s="23"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+    </row>
+    <row r="17" spans="1:11" ht="16.5">
+      <c r="A17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="20">
+        <f t="shared" si="0"/>
+        <v>400000000</v>
+      </c>
+      <c r="C17" s="21">
+        <f t="shared" si="1"/>
+        <v>3257789252</v>
+      </c>
+      <c r="D17" s="23">
+        <v>800000000</v>
+      </c>
+      <c r="E17" s="33">
+        <v>638140781</v>
+      </c>
+      <c r="F17" s="33">
+        <v>945000000</v>
+      </c>
+      <c r="G17" s="33">
+        <v>1500000000</v>
+      </c>
+      <c r="H17" s="33">
+        <v>3257789252</v>
+      </c>
+      <c r="I17" s="33">
+        <v>400000000</v>
+      </c>
+      <c r="J17" s="33">
+        <v>926100000</v>
+      </c>
+      <c r="K17" s="33"/>
+    </row>
+    <row r="18" spans="1:11" ht="16.5">
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="34"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
+    </row>
+    <row r="19" spans="1:11" ht="16.5">
+      <c r="A19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C19" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D19" s="23"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+    </row>
+    <row r="20" spans="1:11" ht="16.5">
+      <c r="A20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C20" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D20" s="23"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+    </row>
+    <row r="21" spans="1:11" ht="16.5">
+      <c r="A21" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="20">
+        <f t="shared" si="0"/>
+        <v>4190331415</v>
+      </c>
+      <c r="C21" s="21">
+        <f t="shared" si="1"/>
+        <v>4190331415</v>
+      </c>
+      <c r="D21" s="23">
+        <v>4190331415</v>
+      </c>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+    </row>
+    <row r="22" spans="1:11" ht="16.5">
+      <c r="A22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="20">
+        <f t="shared" si="0"/>
+        <v>2814200845</v>
+      </c>
+      <c r="C22" s="21">
+        <f t="shared" si="1"/>
+        <v>2814200845</v>
+      </c>
+      <c r="D22" s="23">
+        <v>2814200845</v>
+      </c>
+      <c r="E22" s="33"/>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+    </row>
+    <row r="23" spans="1:11" ht="16.5">
+      <c r="A23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C23" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D23" s="23"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="33"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+    </row>
+    <row r="24" spans="1:11" ht="16.5">
+      <c r="A24" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C24" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D24" s="23"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="33"/>
+      <c r="G24" s="33"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+    </row>
+    <row r="25" spans="1:11" ht="16.5">
+      <c r="A25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C25" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D25" s="23"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="33"/>
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+    </row>
+    <row r="26" spans="1:11" ht="16.5">
+      <c r="A26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="34"/>
+      <c r="C26" s="35"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="32"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
+    </row>
+    <row r="27" spans="1:11" ht="16.5">
+      <c r="A27" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B27" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C27" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D27" s="23"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="33"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+    </row>
+    <row r="28" spans="1:11" ht="16.5">
+      <c r="A28" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C28" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="23"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="33"/>
+    </row>
+    <row r="29" spans="1:11" ht="16.5">
+      <c r="A29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C29" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D29" s="23"/>
+      <c r="E29" s="33"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+    </row>
+    <row r="30" spans="1:11" ht="16.5">
+      <c r="A30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B30" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C30" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D30" s="23"/>
+      <c r="E30" s="33"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+    </row>
+    <row r="31" spans="1:11" ht="16.5">
+      <c r="A31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C31" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D31" s="23"/>
+      <c r="E31" s="33"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="33"/>
+    </row>
+    <row r="32" spans="1:11" ht="16.5">
+      <c r="A32" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B32" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C32" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D32" s="23"/>
+      <c r="E32" s="33"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+    </row>
+    <row r="33" spans="1:11" ht="16.5">
+      <c r="A33" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B33" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C33" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D33" s="23"/>
+      <c r="E33" s="33"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+    </row>
+    <row r="34" spans="1:11" ht="16.5">
+      <c r="A34" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B34" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C34" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="23"/>
+      <c r="E34" s="33"/>
+      <c r="F34" s="33"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+    </row>
+    <row r="35" spans="1:11" ht="16.5">
+      <c r="A35" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" s="34"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="32"/>
+      <c r="F35" s="32"/>
+      <c r="G35" s="32"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
+      <c r="J35" s="32"/>
+      <c r="K35" s="32"/>
+    </row>
+    <row r="36" spans="1:11" ht="16.5">
+      <c r="A36" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C36" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D36" s="23"/>
+      <c r="E36" s="33"/>
+      <c r="F36" s="33"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+    </row>
+    <row r="37" spans="1:11" ht="16.5">
+      <c r="A37" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C37" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D37" s="23"/>
+      <c r="E37" s="33"/>
+      <c r="F37" s="33"/>
+      <c r="G37" s="33"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="33"/>
+      <c r="K37" s="33"/>
+    </row>
+    <row r="38" spans="1:11" ht="16.5">
+      <c r="A38" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B38" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C38" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D38" s="23"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="33"/>
+    </row>
+    <row r="39" spans="1:11" ht="16.5">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C39" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D39" s="23"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+    </row>
+    <row r="40" spans="1:11" ht="16.5">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C40" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D40" s="23"/>
+      <c r="E40" s="33"/>
+      <c r="F40" s="33"/>
+      <c r="G40" s="33"/>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
+      <c r="J40" s="33"/>
+      <c r="K40" s="33"/>
+    </row>
+    <row r="41" spans="1:11" ht="16.5">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C41" s="21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="D41" s="23">
+        <f>G41</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="33">
+        <f>E16*10</f>
+        <v>0</v>
+      </c>
+      <c r="F41" s="33"/>
+      <c r="G41" s="33">
+        <f>G16*10</f>
+        <v>0</v>
+      </c>
+      <c r="H41" s="33"/>
+      <c r="I41" s="33"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="33"/>
+    </row>
+    <row r="42" spans="1:11" ht="16.5">
+      <c r="A42" s="8"/>
+      <c r="B42" s="24"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="32"/>
+      <c r="F42" s="32"/>
+      <c r="G42" s="32"/>
+      <c r="H42" s="32"/>
+      <c r="I42" s="32"/>
+      <c r="J42" s="32"/>
+      <c r="K42" s="32"/>
+    </row>
+    <row r="43" spans="1:11">
+      <c r="B43" s="14"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="16"/>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="B44" s="14"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="16"/>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="B45" s="14"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="16"/>
+    </row>
+    <row r="46" spans="1:11">
+      <c r="B46" s="14"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="16"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="B47" s="14"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="16"/>
+    </row>
+    <row r="48" spans="1:11">
+      <c r="B48" s="14"/>
+      <c r="C48" s="15"/>
+      <c r="D48" s="16"/>
+    </row>
+    <row r="49" spans="2:4">
+      <c r="B49" s="14"/>
+      <c r="C49" s="15"/>
+      <c r="D49" s="16"/>
+    </row>
+    <row r="50" spans="2:4">
+      <c r="B50" s="14"/>
+      <c r="C50" s="15"/>
+      <c r="D50" s="16"/>
+    </row>
+    <row r="51" spans="2:4">
+      <c r="B51" s="14"/>
+      <c r="C51" s="15"/>
+      <c r="D51" s="16"/>
+    </row>
+    <row r="52" spans="2:4">
+      <c r="B52" s="14"/>
+      <c r="C52" s="15"/>
+      <c r="D52" s="16"/>
+    </row>
+    <row r="53" spans="2:4">
+      <c r="B53" s="14"/>
+      <c r="C53" s="15"/>
+      <c r="D53" s="16"/>
+    </row>
+    <row r="54" spans="2:4">
+      <c r="B54" s="14"/>
+      <c r="C54" s="15"/>
+      <c r="D54" s="16"/>
+    </row>
+    <row r="55" spans="2:4">
+      <c r="B55" s="14"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="16"/>
+    </row>
+    <row r="56" spans="2:4">
+      <c r="B56" s="14"/>
+      <c r="C56" s="15"/>
+      <c r="D56" s="16"/>
+    </row>
+    <row r="57" spans="2:4">
+      <c r="B57" s="14"/>
+      <c r="C57" s="15"/>
+      <c r="D57" s="16"/>
+    </row>
+    <row r="58" spans="2:4">
+      <c r="B58" s="14"/>
+      <c r="C58" s="15"/>
+      <c r="D58" s="16"/>
+    </row>
+    <row r="59" spans="2:4">
+      <c r="B59" s="14"/>
+      <c r="C59" s="15"/>
+      <c r="D59" s="16"/>
+    </row>
+    <row r="60" spans="2:4">
+      <c r="B60" s="14"/>
+      <c r="C60" s="15"/>
+      <c r="D60" s="16"/>
+    </row>
+    <row r="61" spans="2:4">
+      <c r="B61" s="14"/>
+      <c r="C61" s="15"/>
+      <c r="D61" s="16"/>
+    </row>
+    <row r="62" spans="2:4">
+      <c r="B62" s="14"/>
+      <c r="C62" s="15"/>
+      <c r="D62" s="16"/>
+    </row>
+    <row r="63" spans="2:4">
+      <c r="B63" s="14"/>
+      <c r="C63" s="15"/>
+      <c r="D63" s="16"/>
+    </row>
+    <row r="64" spans="2:4">
+      <c r="B64" s="14"/>
+      <c r="C64" s="15"/>
+      <c r="D64" s="16"/>
+    </row>
+    <row r="65" spans="2:4">
+      <c r="B65" s="14"/>
+      <c r="C65" s="15"/>
+      <c r="D65" s="16"/>
+    </row>
+    <row r="66" spans="2:4">
+      <c r="B66" s="14"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="16"/>
+    </row>
+    <row r="67" spans="2:4">
+      <c r="B67" s="14"/>
+      <c r="C67" s="15"/>
+      <c r="D67" s="16"/>
+    </row>
+    <row r="68" spans="2:4">
+      <c r="B68" s="14"/>
+      <c r="C68" s="15"/>
+      <c r="D68" s="16"/>
+    </row>
+    <row r="69" spans="2:4">
+      <c r="B69" s="14"/>
+      <c r="C69" s="15"/>
+      <c r="D69" s="16"/>
+    </row>
+    <row r="70" spans="2:4">
+      <c r="B70" s="14"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="16"/>
+    </row>
+    <row r="71" spans="2:4">
+      <c r="B71" s="14"/>
+      <c r="C71" s="15"/>
+      <c r="D71" s="16"/>
+    </row>
+    <row r="72" spans="2:4">
+      <c r="B72" s="14"/>
+      <c r="C72" s="15"/>
+      <c r="D72" s="16"/>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="B73" s="14"/>
+      <c r="C73" s="15"/>
+      <c r="D73" s="16"/>
+    </row>
+    <row r="74" spans="2:4">
+      <c r="B74" s="14"/>
+      <c r="C74" s="15"/>
+      <c r="D74" s="16"/>
+    </row>
+    <row r="75" spans="2:4">
+      <c r="B75" s="14"/>
+      <c r="C75" s="15"/>
+      <c r="D75" s="16"/>
+    </row>
+    <row r="76" spans="2:4">
+      <c r="B76" s="14"/>
+      <c r="C76" s="15"/>
+      <c r="D76" s="16"/>
+    </row>
+    <row r="77" spans="2:4">
+      <c r="B77" s="14"/>
+      <c r="C77" s="15"/>
+      <c r="D77" s="16"/>
+    </row>
+    <row r="78" spans="2:4">
+      <c r="B78" s="14"/>
+      <c r="C78" s="15"/>
+      <c r="D78" s="16"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>